--- a/revision_editorial_odontologia.xlsx
+++ b/revision_editorial_odontologia.xlsx
@@ -11,6 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mayúsculas corregidas" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sin puntuación final" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opciones truncadas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tildes corregidas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ortografía - por qué no seguí" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -518,171 +520,240 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="4" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Tildes faltantes restituidas (palabras sin ambigüedad, ver metodología abajo)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>169</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Pendiente de tu revisión (no se tocó el JSON)</t>
-        </is>
-      </c>
+      <c r="A9" s="3" t="inlineStr"/>
       <c r="B9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Preguntas sin puntuación final (?, ., ! o :)</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>381</v>
-      </c>
+          <t>Pendiente de tu revisión (no se tocó el JSON)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>Preguntas sin puntuación final (?, ., ! o :)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>Opciones de respuesta que parecen cortadas a mitad de oración</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B12" s="4" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="4" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Revisado, sin cambios necesarios</t>
-        </is>
-      </c>
+      <c r="A13" s="3" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Capítulos (15 nombres únicos, sin inconsistencias de formato)</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+          <t>Revisado, sin cambios necesarios</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>Capítulos (15 nombres únicos, sin inconsistencias de formato)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>Campo 'caso' (32 preguntas con viñeta clínica): sin MAYÚSCULAS ni espacios dobles</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Notas:</t>
-        </is>
-      </c>
+      <c r="A17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>- Las 143 conversiones de MAYÚSCULAS preservan siglas médicas conocidas (VIH, EPOC, IECA, AINE, IMAO, etc.) en mayúscula.</t>
+          <t>Notas:</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>- Segunda pasada (2026-08-25): se revisaron a mano las 143 conversiones y se corrigieron 11 errores puntuales que la conversión</t>
+          <t>- Las 143 conversiones de MAYÚSCULAS preservan siglas médicas conocidas (VIH, EPOC, IECA, AINE, IMAO, etc.) en mayúscula.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  automática había dejado: nombres propios que quedaron en minúscula (Fallot, Down, Graves-Basedow), 'de' capitalizada por error</t>
+          <t>- Segunda pasada (2026-08-25): se revisaron a mano las 143 conversiones y se corrigieron 11 errores puntuales que la conversión</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  después de una abreviatura con punto ('Enf.', 'gl.'), dos siglas de fármacos no reconocidas (DDAVP, EACA) y un caso donde la</t>
+          <t xml:space="preserve">  automática había dejado: nombres propios que quedaron en minúscula (Fallot, Down, Graves-Basedow), 'de' capitalizada por error</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  falta de espacio en el original ('INR:(RAZÓN...') hizo que el conversor no reconociera la sigla INR. Esta pestaña ya refleja</t>
+          <t xml:space="preserve">  después de una abreviatura con punto ('Enf.', 'gl.'), dos siglas de fármacos no reconocidas (DDAVP, EACA) y un caso donde la</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  el texto final corregido.</t>
+          <t xml:space="preserve">  falta de espacio en el original ('INR:(RAZÓN...') hizo que el conversor no reconociera la sigla INR. Esta pestaña ya refleja</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>- El texto ALL CAPS original casi nunca traía tildes (ej. 'ACCION' en vez de 'ACCIÓN'); pasar a minúsculas no restituye acentos</t>
+          <t xml:space="preserve">  el texto final corregido.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  que ya faltaban en el original — es una limpieza de formato, no una corrección ortográfica del contenido.</t>
+          <t>- El texto ALL CAPS original casi nunca traía tildes (ej. 'ACCION' en vez de 'ACCIÓN'); pasar a minúsculas no restituye acentos</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>- Las opciones que EMPIEZAN en minúscula (~960 en todo el banco) no se tocaron: en la mayoría de los casos son continuación</t>
+          <t xml:space="preserve">  que ya faltaban en el original — es una limpieza de formato, no una corrección ortográfica del contenido.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  gramatical del enunciado (ej. enunciado 'El mecanismo de acción es:' + opción 'menor al normal'), así que la minúscula ahí</t>
+          <t>- Las opciones que EMPIEZAN en minúscula (~960 en todo el banco) no se tocaron: en la mayoría de los casos son continuación</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  es correcta, no un error. Si querés, puedo revisarlas caso por caso en una próxima pasada.</t>
+          <t xml:space="preserve">  gramatical del enunciado (ej. enunciado 'El mecanismo de acción es:' + opción 'menor al normal'), así que la minúscula ahí</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>- Pregunta #137: las opciones C y D tienen el mismo texto exacto — no es un tema de estilo, posible error de carga del banco,</t>
+          <t xml:space="preserve">  es correcta, no un error. Si querés, puedo revisarlas caso por caso en una próxima pasada.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>- Pregunta #137: las opciones C y D tienen el mismo texto exacto — no es un tema de estilo, posible error de carga del banco,</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">  se lo marco aparte para que lo revises con la fuente original.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Ortografía (2026-08-25): se restituyeron 169 tildes faltantes (99 palabras distintas, ver pestaña 'Tildes corregidas'), usando</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>el corrector hunspell (diccionario es_ES) y aplicando SOLO los casos donde la palabra original no tenía ningún acento y existía</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>una única variante acentuada posible (ej. 'accion' → 'acción'). No se tocaron palabras que ya tenían algún acento (para no</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>arriesgar revertir uno correcto) ni las siglas/nombres científicos en mayúscula (Candida albicans, unidades como 'mUI', etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>No se hizo una corrección general de errores de tipeo (más allá de tildes): el diccionario en español no reconoce gran parte</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>del vocabulario médico/odontológico del banco, así que sus sugerencias de 'corrección' para esas palabras suelen ser palabras</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>reales pero completamente equivocadas — ver pestaña 'Ortografía - por qué no seguí' con ejemplos concretos de por qué aplicar</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>esas sugerencias a ciegas hubiera sido peligroso en contenido de examen.</t>
         </is>
       </c>
     </row>
@@ -11553,4 +11624,3071 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D142"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Campo</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Antes</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Los pacientes con enfermedad cardiovascular son mas sensibles a la accion de la adrenalina, en estos hay que utilizar siempre que no este contraindicado, dosis menores de anestesicos con vasoconstrictor y a la dilucion mas baja de adrenaliana 1:200.000, no se podran usar mas de:</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Los pacientes con enfermedad cardiovascular son mas sensibles a la acción de la adrenalina, en estos hay que utilizar siempre que no este contraindicado, dosis menores de anestésicos con vasoconstrictor y a la dilución mas baja de adrenaliana 1:200.000, no se podrán usar mas de:</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>En casos tipicos el dolor puede irradiarse al hombro derecho</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>En casos típicos el dolor puede irradiarse al hombro derecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>opcion A</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Los nitratos sublingulales y el nifedipino, proporcionan alivio rapido</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Los nitratos sublingulales y el nifedipino, proporcionan alivio rápido</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>opcion B</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Si estos pacientes son portadores de bypass coronarios necesitan proteccion antibiotica contra la endocarditis</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Si estos pacientes son portadores de bypass coronarios necesitan protección antibiótica contra la endocarditis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>La intervencion dental exigira la colaboracion del médico del paciente</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>La intervención dental exigirá la colaboración del médico del paciente</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Los barbituricos son peligrosos</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Los barbitúricos son peligrosos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>opcion E</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Deben ser sedados con benzodiacepinas desde un dia antes de la cita</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Deben ser sedados con benzodiacepinas desde un día antes de la cita</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Clinicamente en el infarto de miocardio hay hipertension</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Clinicamente en el infarto de miocardio hay hipertensión</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Los vasoconstrictores estan contraindicados en forma absoluta en las siguientes patologias excepto de forma relativa en:</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Los vasoconstrictores están contraindicados en forma absoluta en las siguientes patologías excepto de forma relativa en:</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Ritmo cardiaco extrasinusales es un factor predictivo de riesgo mayor</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Ritmo cardíaco extrasinusales es un factor predictivo de riesgo mayor</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Marque la respuesta FALSA. En los pacientes con patología cardiaca y vascular corregida quirúrgicamente:</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Marque la respuesta FALSA. En los pacientes con patología cardíaca y vascular corregida quirúrgicamente:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Marque la respuesta FALSA. En un paciente con insuficiencia cardiaca:</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Marque la respuesta FALSA. En un paciente con insuficiencia cardíaca:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>opcion E</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Ritmo cardiaco extrasinusal es un factor predictivo de riesgo mayor</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Ritmo cardíaco extrasinusal es un factor predictivo de riesgo mayor</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>¿Cuál de los siguientes factores es un factor predictivo menor del riesgo cardiaco?</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>¿Cuál de los siguientes factores es un factor predictivo menor del riesgo cardíaco?</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>opcion E</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Insuficiencia cardiaca descompensada.</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Insuficiencia cardíaca descompensada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>opcion B</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Los farmacos antagonistas del calcio que se emplean como antihipertensivos pueden producir hiperplasia gingival.</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Los fármacos antagonistas del calcio que se emplean como antihipertensivos pueden producir hiperplasia gingival.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>opcion E</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Los ritmos cardiacos extraauriculares son un factor predictivo de riesgo mayor.</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Los ritmos cardíacos extraauriculares son un factor predictivo de riesgo mayor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>opcion E</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Ritmo cardiaco extrasinusales es un factor predictivo de riesgo mayor</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Ritmo cardíaco extrasinusales es un factor predictivo de riesgo mayor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>opcion E</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>arritmia cardiaca</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>arritmia cardíaca</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>PIGMENTACION CUTANEA (848MN pigmentacion intrinseca gris )</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>PIGMENTACION CUTANEA (848MN pigmentación intrínseca gris )</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>MN 632; vademecum; fenomeno Raynaud</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>MN 632; vademécum; fenómeno Raynaud</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>opcion E</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Extremidades frias</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Extremidades frías</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Marque la respuesta FALSA. En un paciente con insuficiencia cardiaca:</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Marque la respuesta FALSA. En un paciente con insuficiencia cardíaca:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Cuál de estos efectos adversos medicamentosos NO es propio de los pacientes con insuficiencia cardiaca? MN845</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Cuál de estos efectos adversos medicamentosos NO es propio de los pacientes con insuficiencia cardíaca? MN845</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>98</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>opcion B</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Si el tratamiento es urgente deber· ser siempre conservador “MC623 si es urgente el tratamiento será conservador mediante ATB y analgesico”</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Si el tratamiento es urgente deber· ser siempre conservador “MC623 si es urgente el tratamiento será conservador mediante ATB y analgésico”</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>120mm Hg emergencia “lesion org.diana”/urgencia</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>120mm Hg emergencia “lesión org.diana”/urgencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>114</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>areas de microinfarto</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>áreas de microinfarto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>131</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>En un paciente con tetralogia de Fallot que consiste en una severa anomalia anatomica, es falso que presente:</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>En un paciente con tetralogía de Fallot que consiste en una severa anomalía anatómica, es falso que presente:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>131</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Hipertrofia del ventriculo derecho</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Hipertrofia del ventrículo derecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>132</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>La cardipoatia congenita más frecuente es:</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>La cardipoatia congénita más frecuente es:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>133</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Se observa frecuentemente en niños con sindrome de Down</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Se observa frecuentemente en niños con síndrome de Down</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>134</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>En las anomalias anatomicas, incluidas en la tetralogia de Fallot no esta incluida:</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>En las anomalías anatómicas, incluidas en la tetralogía de Fallot no esta incluida:</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>134</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Hipertrofia del ventriculo derecho</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Hipertrofia del ventrículo derecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>135</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Respecto a las consideraciones dentales en las cardiopatias congenitas es incorrecto:</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Respecto a las consideraciones dentales en las cardiopatias congénitas es incorrecto:</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>135</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>opcion A</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Se pueden asociar a una erupcion retarsada de ladenticion temporal y permanente</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Se pueden asociar a una erupción retarsada de ladenticion temporal y permanente</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>135</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>opcion B</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Alteraciones en la posicion de los dientes e hipoplasia del esmalte</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Alteraciones en la posición de los dientes e hipoplasia del esmalte</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>135</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Se pueden desarrollar abcesos cerebrales despues de infecciones dentales</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Se pueden desarrollar abcesos cerebrales después de infecciones dentales</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>136</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Necesariamente hay que prescribir proteccion antibiotica para la endocarditis</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Necesariamente hay que prescribir protección antibiótica para la endocarditis</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>136</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>opcion E</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Los trabajos hay que realizarlos en posicion supina.</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Los trabajos hay que realizarlos en posición supina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>139</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>opcion B</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>El cardiologo dará antibiotico</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>El cardiólogo dará antibiótico</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>139</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Dar antibioticos hasta que cure</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Dar antibióticos hasta que cure</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>155</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Mieloma multiple</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Mieloma múltiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>157</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>opcion E</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>TDAH ( trastorno por deficit de atencion)</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>TDAH ( trastorno por déficit de atención)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>158</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>opcion B</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Hipertiroidismo apatico</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Hipertiroidismo apático</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>159</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Cual de estas etiologias es la mas frecuente en el hipotiroidismo congetito:</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Cual de estas etiologías es la mas frecuente en el hipotiroidismo congetito:</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>160</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Solicitar una puncion por aspiracion de gl. tiroides</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Solicitar una punción por aspiración de gl. tiroides</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n">
+        <v>161</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Entre las enf. de la hipofisis posterior o neurohipofisis estan:</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Entre las enf. de la hipófisis posterior o neurohipofisis están:</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n">
+        <v>161</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Diabetes insipida</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Diabetes insípida</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n">
+        <v>216</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Que medicamento NO administrarias en EPOC</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Que medicamento NO administrarías en EPOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n">
+        <v>217</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>pag 656 cuadro MACHUCA NUEVO</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>pág 656 cuadro MACHUCA NUEVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n">
+        <v>217</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>midazolam midazolam dosis bajas via oral Inma</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>midazolam midazolam dosis bajas vía oral Inma</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n">
+        <v>235</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Si hablamos de un paciente menor de 35 años con niveles elevados de IgE y pruebas cutáneas positivas a una alergeno específico estamos hablando de un paciente afecto de:</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Si hablamos de un paciente menor de 35 años con niveles elevados de IgE y pruebas cutáneas positivas a una alérgeno específico estamos hablando de un paciente afecto de:</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n">
+        <v>283</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>pag 609-610-1132 MACHUCA NUEVO. osteonecrosis por bisfosfonatos 14 DIAS ANTES 7 DIAS DESPUES</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>pág 609-610-1132 MACHUCA NUEVO. osteonecrosis por bisfosfonatos 14 DIAS ANTES 7 DIAS DESPUES</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n">
+        <v>284</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Eritema, úlcera y puede consumir liquidos</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Eritema, úlcera y puede consumir líquidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n">
+        <v>314</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Eritema, ulcera y puede consumir liquidos</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Eritema, ulcera y puede consumir líquidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n">
+        <v>318</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>opcion E</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>Trasplante autólogo de medula ósea</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Trasplante autólogo de médula ósea</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n">
+        <v>339</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>pag 610 Machuca Nuevo</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>pág 610 Machuca Nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n">
+        <v>354</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>opcion A</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>uso de dentrificos adaptados (dentrificos de xerostomia ,con alto contenido de fluor ,xialogogos)</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>uso de dentrificos adaptados (dentrificos de xerostomia ,con alto contenido de flúor ,xialogogos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n">
+        <v>414</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>pag 609 MACHUCA NUEVO</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>pág 609 MACHUCA NUEVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n">
+        <v>429</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>pag 799 MACHUCA NUEVO</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>pág 799 MACHUCA NUEVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n">
+        <v>432</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>pag 804 MACHUCA NUEVO</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>pág 804 MACHUCA NUEVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>436</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>opcion E</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>seudoxantoma clasico</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>seudoxantoma clásico</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>444</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>pag 805 MACHUCA NUEVO. pag 807 tabla 5</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>pág 805 MACHUCA NUEVO. pág 807 tabla 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n">
+        <v>445</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>La agregacion plaquetaria en el coagulo se inicia por:</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>La agregación plaquetaria en el coagulo se inicia por:</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>449</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Si el sangrado post-extracción es a nivel óseo, nunca se usará cera de hueso en el alveolo</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Si el sangrado post-extracción es a nivel óseo, nunca se usará cera de hueso en el alvéolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n">
+        <v>501</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>opcion A</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Lavado del alveolo con 0,3mg/kg de peso de desmopresina</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Lavado del alvéolo con 0,3mg/kg de peso de desmopresina</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n">
+        <v>501</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>opcion B</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>Lavado del alveolo con 0,3mg/kg de peso de desmopresina y sutura del</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Lavado del alvéolo con 0,3mg/kg de peso de desmopresina y sutura del</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n">
+        <v>501</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>Lavado del alveolo con 5ml de ácido tranexámico</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Lavado del alvéolo con 5ml de ácido tranexámico</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="n">
+        <v>501</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>Lavado del alveolo con 5ml de ácido tranexámico y sutura del alveolo</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Lavado del alvéolo con 5ml de ácido tranexámico y sutura del alvéolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n">
+        <v>516</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>¿Cual es el mecanismo de accion de los farmacos derivados cumarinicos, como el sintrom?</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>¿Cual es el mecanismo de acción de los fármacos derivados cumarinicos, como el sintrom?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>516</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>opcion A</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Activan los depositos de vitamina K</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Activan los depósitos de vitamina K</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n">
+        <v>516</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>opcion B</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>Potencian la accion de la antitrombina (heparina)</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Potencian la acción de la antitrombina (heparina)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>522</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>De los siguientes farmacos cual es antiagregante plaquetario</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>De los siguientes fármacos cual es antiagregante plaquetario</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>522</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>opcion A</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>acido acetil salicílico</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>ácido acetil salicílico</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n">
+        <v>525</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>opcion A</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Dos dias</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Dos días</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n">
+        <v>525</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>opcion B</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>Tres dias</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Tres días</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n">
+        <v>525</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Cuatro dias</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Cuatro días</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="n">
+        <v>525</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>Siete dias</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Siete días</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="n">
+        <v>525</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>opcion E</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Ocho dias</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Ocho días</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n">
+        <v>526</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>De los siguientes farmacos cual es antiagregante plaquetario</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>De los siguientes fármacos cual es antiagregante plaquetario</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="n">
+        <v>534</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>opcion A</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Apósito de acido amino Capróico (antifibrinolitico)</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Apósito de ácido amino Capróico (antifibrinolitico)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="n">
+        <v>544</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>cloranfenicol puede causar anemia aplasica; pag 833 MACHUCA NEUVO</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>cloranfenicol puede causar anemia aplasica; pág 833 MACHUCA NEUVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n">
+        <v>559</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Pedro Diz pag 283; 563 cap VIH machuca nuevo</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Pedro Diz pág 283; 563 cap VIH machuca nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="n">
+        <v>560</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>comunes en todas las anemias pag 832 MACHUCA NUEVO</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>comunes en todas las anemias pág 832 MACHUCA NUEVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="n">
+        <v>561</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>pag 575 MACHUCA NUEVO</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>pág 575 MACHUCA NUEVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="n">
+        <v>584</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>Herpes zoster</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Herpes zóster</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n">
+        <v>589</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Señale qué lesión está menos comunmente asociada a la infección por VIH</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Señale qué lesión está menos comúnmente asociada a la infección por VIH</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="n">
+        <v>606</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>opcion E</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Herpes zoster</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Herpes zóster</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="n">
+        <v>684</v>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Identifica cual de las siguientes no se considera como una complicacion de una hepatitis aguda virica:</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Identifica cual de las siguientes no se considera como una complicación de una hepatitis aguda vírica:</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="n">
+        <v>684</v>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>opcion A</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>Cirrosis hepatica</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Cirrosis hepática</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n">
+        <v>684</v>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>opcion B</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>Pancreatitis cronica</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Pancreatitis crónica</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="n">
+        <v>684</v>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>Insuficiencia hepatica</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>Insuficiencia hepática</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n">
+        <v>684</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Cancer de higado</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Cancer de hígado</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="n">
+        <v>685</v>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>Mediante la palpacion del higado</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Mediante la palpación del hígado</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n">
+        <v>697</v>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>opcion A</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>El ser varon es factor de riesgo</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>El ser varón es factor de riesgo</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n">
+        <v>762</v>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>recomendado lorazepam unico</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>recomendado lorazepam único</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="n">
+        <v>778</v>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>aguda o cronica</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>aguda o crónica</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="n">
+        <v>829</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>Marque la correcta. En paciente con hemodiálisis cronica</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Marque la correcta. En paciente con hemodiálisis crónica</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="n">
+        <v>830</v>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>opcion B</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>Riesgo de infeccion, VHB, VHC, citomegalovirus, etc.</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Riesgo de infección, VHB, VHC, citomegalovirus, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="n">
+        <v>831</v>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>Propia de la patologia renal</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Propia de la patología renal</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="n">
+        <v>839</v>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>pag 748 MACHUCA NUEVO</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>pág 748 MACHUCA NUEVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="n">
+        <v>839</v>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>opcion A</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>Salicilatos riesgo de sangrado gastrico</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Salicilatos riesgo de sangrado gástrico</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="n">
+        <v>949</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>opcion A</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>Psicosis maniaca depresiva.</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Psicosis maníaca depresiva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="n">
+        <v>990</v>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>Las papilas interceptarias no suelen ser afectadas.</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>Las papilas interceptarías no suelen ser afectadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>pag 756 MACHUCA NUEVO</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>pág 756 MACHUCA NUEVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="n">
+        <v>1019</v>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>segundo trimestre. pag 766 MACHUCA NUEVO</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>segundo trimestre. pág 766 MACHUCA NUEVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="n">
+        <v>1033</v>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>c caracterizados por un incremento de las poblaciones de Gramnegativos anaerobicos</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>c caracterizados por un incremento de las poblaciones de Gramnegativos anaeróbicos</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="n">
+        <v>1067</v>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>bibliografia</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>pag 110-111 MACHUCA NUEVO</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>pág 110-111 MACHUCA NUEVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="n">
+        <v>1070</v>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>opcion A</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>Si el paciente mantiene el ritmo cardiaco</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>Si el paciente mantiene el ritmo cardíaco</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="n">
+        <v>1072</v>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>opcion A</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>acido epsilon amino caproico</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>ácido epsilon amino caproico</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="n">
+        <v>1072</v>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>acido tranexamico</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>ácido tranexamico</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n">
+        <v>1093</v>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>opcion E</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>Si no se palpa el pulso comenzar de inmediato la compresión cardiaca externa.</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>Si no se palpa el pulso comenzar de inmediato la compresión cardíaca externa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="n">
+        <v>1126</v>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>masaje cardiaco</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>masaje cardíaco</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="n">
+        <v>1135</v>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>Acercar el oido y mejilla a la boca del paciente para comprobar si hay respiración</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>Acercar el oído y mejilla a la boca del paciente para comprobar si hay respiración</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="n">
+        <v>1139</v>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>opcion B</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>Reduce el tono muscular liso pag 626 y 627</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>Reduce el tono muscular liso pág 626 y 627</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="n">
+        <v>1146</v>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>Desfibrilación electrica.</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>Desfibrilación eléctrica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="n">
+        <v>1160</v>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>Desfibrilación electrica.</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>Desfibrilación eléctrica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="n">
+        <v>1162</v>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>opcion B</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>Nunca se debe administrar analgesico pues enmascaría los síntomas</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>Nunca se debe administrar analgésico pues enmascaría los síntomas</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>caso</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. Mujer de 60 años acude para sanear la boca, tiene removibles arriba y abajo desde hace 15 años en los que no ha ido al dentista más que para quitarse algún diente por dolor o infección y alguno se le ha roto. Quiere que se le extraigan todos y no tener más complicaciones y el nefrólogo la metió en la lista de transplante Sin alergia HTA de larga evolucion, IRC necesita un transplante y tiene diálisis martes jueves y sábados diabetics tipo 1 dislipemia EPOC Gold 1 colescistectomia y apendicitis. Toma ramipril fueosemida atorvastatina usa insulina de acción lenta a las 22H omeprazol paracetamol budosomida-formoterol bromuro de ipiatropo y salbutamol. Tiene ausencias arriba y abajo restos en 13-15-25-47 caries en 14 23 24-35-43-45 con fistula acúmulo moderado mala higiene hipo salía estomatitis protretica enf perio con movilidad de remanentes grado 2 y 3. Y ortopanto con lesión radio lúcida foco periapiacal entre 45-46</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. Mujer de 60 años acude para sanear la boca, tiene removibles arriba y abajo desde hace 15 años en los que no ha ido al dentista más que para quitarse algún diente por dolor o infección y alguno se le ha roto. Quiere que se le extraigan todos y no tener más complicaciones y el nefrólogo la metió en la lista de transplante Sin alergia HTA de larga evolución, IRC necesita un transplante y tiene diálisis martes jueves y sábados diabetics tipo 1 dislipemia EPOC Gold 1 colescistectomia y apendicitis. Toma ramipril fueosemida atorvastatina usa insulina de acción lenta a las 22H omeprazol paracetamol budosomida-formoterol bromuro de ipiatropo y salbutamol. Tiene ausencias arriba y abajo restos en 13-15-25-47 caries en 14 23 24-35-43-45 con fistula acúmulo moderado mala higiene hipo salía estomatitis protretica enf perio con movilidad de remanentes grado 2 y 3. Y ortopanto con lesión radio lúcida foco periapiacal entre 45-46</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>caso</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. Mujer de 60 años acude para sanear la boca, tiene removibles arriba y abajo desde hace 15 años en los que no ha ido al dentista más que para quitarse algún diente por dolor o infección y alguno se le ha roto. Quiere que se le extraigan todos y no tener más complicaciones y el nefrólogo la metió en la lista de transplante Sin alergia HTA de larga evolucion, IRC necesita un transplante y tiene diálisis martes jueves y sábados diabetics tipo 1 dislipemia EPOC Gold 1 colescistectomia y apendicitis. Toma ramipril fueosemida atorvastatina usa insulina de acción lenta a las 22H omeprazol paracetamol budosomida-formoterol bromuro de ipiatropo y salbutamol. Tiene ausencias arriba y abajo restos en 13-15-25-47 caries en 14 23 24-35-43-45 con fistula acúmulo moderado mala higiene hipo salía estomatitis protretica enf perio con movilidad de remanentes grado 2 y 3. Y ortopanto con lesión radio lúcida foco periapiacal entre 45-46</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. Mujer de 60 años acude para sanear la boca, tiene removibles arriba y abajo desde hace 15 años en los que no ha ido al dentista más que para quitarse algún diente por dolor o infección y alguno se le ha roto. Quiere que se le extraigan todos y no tener más complicaciones y el nefrólogo la metió en la lista de transplante Sin alergia HTA de larga evolución, IRC necesita un transplante y tiene diálisis martes jueves y sábados diabetics tipo 1 dislipemia EPOC Gold 1 colescistectomia y apendicitis. Toma ramipril fueosemida atorvastatina usa insulina de acción lenta a las 22H omeprazol paracetamol budosomida-formoterol bromuro de ipiatropo y salbutamol. Tiene ausencias arriba y abajo restos en 13-15-25-47 caries en 14 23 24-35-43-45 con fistula acúmulo moderado mala higiene hipo salía estomatitis protretica enf perio con movilidad de remanentes grado 2 y 3. Y ortopanto con lesión radio lúcida foco periapiacal entre 45-46</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="n">
+        <v>1173</v>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>caso</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. Mujer de 60 años acude para sanear la boca, tiene removibles arriba y abajo desde hace 15 años en los que no ha ido al dentista más que para quitarse algún diente por dolor o infección y alguno se le ha roto. Quiere que se le extraigan todos y no tener más complicaciones y el nefrólogo la metió en la lista de transplante Sin alergia HTA de larga evolucion, IRC necesita un transplante y tiene diálisis martes jueves y sábados diabetics tipo 1 dislipemia EPOC Gold 1 colescistectomia y apendicitis. Toma ramipril fueosemida atorvastatina usa insulina de acción lenta a las 22H omeprazol paracetamol budosomida-formoterol bromuro de ipiatropo y salbutamol. Tiene ausencias arriba y abajo restos en 13-15-25-47 caries en 14 23 24-35-43-45 con fistula acúmulo moderado mala higiene hipo salía estomatitis protretica enf perio con movilidad de remanentes grado 2 y 3. Y ortopanto con lesión radio lúcida foco periapiacal entre 45-46</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. Mujer de 60 años acude para sanear la boca, tiene removibles arriba y abajo desde hace 15 años en los que no ha ido al dentista más que para quitarse algún diente por dolor o infección y alguno se le ha roto. Quiere que se le extraigan todos y no tener más complicaciones y el nefrólogo la metió en la lista de transplante Sin alergia HTA de larga evolución, IRC necesita un transplante y tiene diálisis martes jueves y sábados diabetics tipo 1 dislipemia EPOC Gold 1 colescistectomia y apendicitis. Toma ramipril fueosemida atorvastatina usa insulina de acción lenta a las 22H omeprazol paracetamol budosomida-formoterol bromuro de ipiatropo y salbutamol. Tiene ausencias arriba y abajo restos en 13-15-25-47 caries en 14 23 24-35-43-45 con fistula acúmulo moderado mala higiene hipo salía estomatitis protretica enf perio con movilidad de remanentes grado 2 y 3. Y ortopanto con lesión radio lúcida foco periapiacal entre 45-46</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>caso</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. Mujer de 60 años acude para sanear la boca, tiene removibles arriba y abajo desde hace 15 años en los que no ha ido al dentista más que para quitarse algún diente por dolor o infección y alguno se le ha roto. Quiere que se le extraigan todos y no tener más complicaciones y el nefrólogo la metió en la lista de transplante Sin alergia HTA de larga evolucion, IRC necesita un transplante y tiene diálisis martes jueves y sábados diabetics tipo 1 dislipemia EPOC Gold 1 colescistectomia y apendicitis. Toma ramipril fueosemida atorvastatina usa insulina de acción lenta a las 22H omeprazol paracetamol budosomida-formoterol bromuro de ipiatropo y salbutamol. Tiene ausencias arriba y abajo restos en 13-15-25-47 caries en 14 23 24-35-43-45 con fistula acúmulo moderado mala higiene hipo salía estomatitis protretica enf perio con movilidad de remanentes grado 2 y 3. Y ortopanto con lesión radio lúcida foco periapiacal entre 45-46</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. Mujer de 60 años acude para sanear la boca, tiene removibles arriba y abajo desde hace 15 años en los que no ha ido al dentista más que para quitarse algún diente por dolor o infección y alguno se le ha roto. Quiere que se le extraigan todos y no tener más complicaciones y el nefrólogo la metió en la lista de transplante Sin alergia HTA de larga evolución, IRC necesita un transplante y tiene diálisis martes jueves y sábados diabetics tipo 1 dislipemia EPOC Gold 1 colescistectomia y apendicitis. Toma ramipril fueosemida atorvastatina usa insulina de acción lenta a las 22H omeprazol paracetamol budosomida-formoterol bromuro de ipiatropo y salbutamol. Tiene ausencias arriba y abajo restos en 13-15-25-47 caries en 14 23 24-35-43-45 con fistula acúmulo moderado mala higiene hipo salía estomatitis protretica enf perio con movilidad de remanentes grado 2 y 3. Y ortopanto con lesión radio lúcida foco periapiacal entre 45-46</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="n">
+        <v>1179</v>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>caso</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>CASO 1. Paciente de 25 años de edad, con mal estado oral, dolores generalizados que se acentúan a la percusión en algunos dientes y en general con los cambios de temperatura. Esta nerviosa y agitada tiene mal estado oral la paciente refiere que lo que ocurre es por una ingesta excesiva de alimentos pero su apariencia fisica (aspecto fisico) no se corresponde con sus circunstancias puesto que presenta un aspecto normal, a lo largo de la anamnesis la paciente expresa el deseo que le extraigan todos los dientes y se le coloquen implantes, ya que su saliva es muy ácida e imposibilita las reconstrucciones como en otras veces.</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>CASO 1. Paciente de 25 años de edad, con mal estado oral, dolores generalizados que se acentúan a la percusión en algunos dientes y en general con los cambios de temperatura. Esta nerviosa y agitada tiene mal estado oral la paciente refiere que lo que ocurre es por una ingesta excesiva de alimentos pero su apariencia física (aspecto físico) no se corresponde con sus circunstancias puesto que presenta un aspecto normal, a lo largo de la anamnesis la paciente expresa el deseo que le extraigan todos los dientes y se le coloquen implantes, ya que su saliva es muy ácida e imposibilita las reconstrucciones como en otras veces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="n">
+        <v>1180</v>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>caso</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>CASO 1. Paciente de 25 años de edad, con mal estado oral, dolores generalizados que se acentúan a la percusión en algunos dientes y en general con los cambios de temperatura. Esta nerviosa y agitada tiene mal estado oral la paciente refiere que lo que ocurre es por una ingesta excesiva de alimentos pero su apariencia fisica (aspecto fisico) no se corresponde con sus circunstancias puesto que presenta un aspecto normal, a lo largo de la anamnesis la paciente expresa el deseo que le extraigan todos los dientes y se le coloquen implantes, ya que su saliva es muy ácida e imposibilita las reconstrucciones como en otras veces.</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>CASO 1. Paciente de 25 años de edad, con mal estado oral, dolores generalizados que se acentúan a la percusión en algunos dientes y en general con los cambios de temperatura. Esta nerviosa y agitada tiene mal estado oral la paciente refiere que lo que ocurre es por una ingesta excesiva de alimentos pero su apariencia física (aspecto físico) no se corresponde con sus circunstancias puesto que presenta un aspecto normal, a lo largo de la anamnesis la paciente expresa el deseo que le extraigan todos los dientes y se le coloquen implantes, ya que su saliva es muy ácida e imposibilita las reconstrucciones como en otras veces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="7" t="n">
+        <v>1181</v>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>caso</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>CASO 1. Paciente de 25 años de edad, con mal estado oral, dolores generalizados que se acentúan a la percusión en algunos dientes y en general con los cambios de temperatura. Esta nerviosa y agitada tiene mal estado oral la paciente refiere que lo que ocurre es por una ingesta excesiva de alimentos pero su apariencia fisica (aspecto fisico) no se corresponde con sus circunstancias puesto que presenta un aspecto normal, a lo largo de la anamnesis la paciente expresa el deseo que le extraigan todos los dientes y se le coloquen implantes, ya que su saliva es muy ácida e imposibilita las reconstrucciones como en otras veces.</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>CASO 1. Paciente de 25 años de edad, con mal estado oral, dolores generalizados que se acentúan a la percusión en algunos dientes y en general con los cambios de temperatura. Esta nerviosa y agitada tiene mal estado oral la paciente refiere que lo que ocurre es por una ingesta excesiva de alimentos pero su apariencia física (aspecto físico) no se corresponde con sus circunstancias puesto que presenta un aspecto normal, a lo largo de la anamnesis la paciente expresa el deseo que le extraigan todos los dientes y se le coloquen implantes, ya que su saliva es muy ácida e imposibilita las reconstrucciones como en otras veces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="n">
+        <v>1182</v>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>caso</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>CASO 1. Paciente de 25 años de edad, con mal estado oral, dolores generalizados que se acentúan a la percusión en algunos dientes y en general con los cambios de temperatura. Esta nerviosa y agitada tiene mal estado oral la paciente refiere que lo que ocurre es por una ingesta excesiva de alimentos pero su apariencia fisica (aspecto fisico) no se corresponde con sus circunstancias puesto que presenta un aspecto normal, a lo largo de la anamnesis la paciente expresa el deseo que le extraigan todos los dientes y se le coloquen implantes, ya que su saliva es muy ácida e imposibilita las reconstrucciones como en otras veces.</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>CASO 1. Paciente de 25 años de edad, con mal estado oral, dolores generalizados que se acentúan a la percusión en algunos dientes y en general con los cambios de temperatura. Esta nerviosa y agitada tiene mal estado oral la paciente refiere que lo que ocurre es por una ingesta excesiva de alimentos pero su apariencia física (aspecto físico) no se corresponde con sus circunstancias puesto que presenta un aspecto normal, a lo largo de la anamnesis la paciente expresa el deseo que le extraigan todos los dientes y se le coloquen implantes, ya que su saliva es muy ácida e imposibilita las reconstrucciones como en otras veces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="n">
+        <v>1183</v>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>caso</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>CASO 1. Paciente de 25 años de edad, con mal estado oral, dolores generalizados que se acentúan a la percusión en algunos dientes y en general con los cambios de temperatura. Esta nerviosa y agitada tiene mal estado oral la paciente refiere que lo que ocurre es por una ingesta excesiva de alimentos pero su apariencia fisica (aspecto fisico) no se corresponde con sus circunstancias puesto que presenta un aspecto normal, a lo largo de la anamnesis la paciente expresa el deseo que le extraigan todos los dientes y se le coloquen implantes, ya que su saliva es muy ácida e imposibilita las reconstrucciones como en otras veces.</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>CASO 1. Paciente de 25 años de edad, con mal estado oral, dolores generalizados que se acentúan a la percusión en algunos dientes y en general con los cambios de temperatura. Esta nerviosa y agitada tiene mal estado oral la paciente refiere que lo que ocurre es por una ingesta excesiva de alimentos pero su apariencia física (aspecto físico) no se corresponde con sus circunstancias puesto que presenta un aspecto normal, a lo largo de la anamnesis la paciente expresa el deseo que le extraigan todos los dientes y se le coloquen implantes, ya que su saliva es muy ácida e imposibilita las reconstrucciones como en otras veces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="n">
+        <v>1184</v>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>caso</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. A su consulta acude una mujer de 50 años se aqueja de un dolor intenso en el 22, dicho dolor se acentúa a la percusión y con los cambios de temperatura, la paciente no ha consumido ningún medicamento porque según refiere sufre de una coagulopatía congénita. La historia clinica no refiere mas datos de interés. (fotos intraorales de piezas dentales ninguna lesión en particular)</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. A su consulta acude una mujer de 50 años se aqueja de un dolor intenso en el 22, dicho dolor se acentúa a la percusión y con los cambios de temperatura, la paciente no ha consumido ningún medicamento porque según refiere sufre de una coagulopatía congénita. La historia clínica no refiere mas datos de interés. (fotos intraorales de piezas dentales ninguna lesión en particular)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="n">
+        <v>1185</v>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>caso</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. A su consulta acude una mujer de 50 años se aqueja de un dolor intenso en el 22, dicho dolor se acentúa a la percusión y con los cambios de temperatura, la paciente no ha consumido ningún medicamento porque según refiere sufre de una coagulopatía congénita. La historia clinica no refiere mas datos de interés. (fotos intraorales de piezas dentales ninguna lesión en particular)</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. A su consulta acude una mujer de 50 años se aqueja de un dolor intenso en el 22, dicho dolor se acentúa a la percusión y con los cambios de temperatura, la paciente no ha consumido ningún medicamento porque según refiere sufre de una coagulopatía congénita. La historia clínica no refiere mas datos de interés. (fotos intraorales de piezas dentales ninguna lesión en particular)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="n">
+        <v>1186</v>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>caso</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. A su consulta acude una mujer de 50 años se aqueja de un dolor intenso en el 22, dicho dolor se acentúa a la percusión y con los cambios de temperatura, la paciente no ha consumido ningún medicamento porque según refiere sufre de una coagulopatía congénita. La historia clinica no refiere mas datos de interés. (fotos intraorales de piezas dentales ninguna lesión en particular)</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. A su consulta acude una mujer de 50 años se aqueja de un dolor intenso en el 22, dicho dolor se acentúa a la percusión y con los cambios de temperatura, la paciente no ha consumido ningún medicamento porque según refiere sufre de una coagulopatía congénita. La historia clínica no refiere mas datos de interés. (fotos intraorales de piezas dentales ninguna lesión en particular)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="n">
+        <v>1187</v>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>caso</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. A su consulta acude una mujer de 50 años se aqueja de un dolor intenso en el 22, dicho dolor se acentúa a la percusión y con los cambios de temperatura, la paciente no ha consumido ningún medicamento porque según refiere sufre de una coagulopatía congénita. La historia clinica no refiere mas datos de interés. (fotos intraorales de piezas dentales ninguna lesión en particular)</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. A su consulta acude una mujer de 50 años se aqueja de un dolor intenso en el 22, dicho dolor se acentúa a la percusión y con los cambios de temperatura, la paciente no ha consumido ningún medicamento porque según refiere sufre de una coagulopatía congénita. La historia clínica no refiere mas datos de interés. (fotos intraorales de piezas dentales ninguna lesión en particular)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="n">
+        <v>1188</v>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>caso</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. A su consulta acude una mujer de 50 años se aqueja de un dolor intenso en el 22, dicho dolor se acentúa a la percusión y con los cambios de temperatura, la paciente no ha consumido ningún medicamento porque según refiere sufre de una coagulopatía congénita. La historia clinica no refiere mas datos de interés. (fotos intraorales de piezas dentales ninguna lesión en particular)</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>CASO 2. A su consulta acude una mujer de 50 años se aqueja de un dolor intenso en el 22, dicho dolor se acentúa a la percusión y con los cambios de temperatura, la paciente no ha consumido ningún medicamento porque según refiere sufre de una coagulopatía congénita. La historia clínica no refiere mas datos de interés. (fotos intraorales de piezas dentales ninguna lesión en particular)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="n">
+        <v>1209</v>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>opcion B</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>Paciente con 5 stents cardiacos tras infarto agudo de miocardio hace 2 años</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>Paciente con 5 stents cardíacos tras infarto agudo de miocardio hace 2 años</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="n">
+        <v>1244</v>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>opcion B</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>En exodoncias, se deberían legrar los alveolos meticulosamente</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>En exodoncias, se deberían legrar los alvéolos meticulosamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="n">
+        <v>1251</v>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>En una paciente con una enfermedad autoinmune que toma 7.5mg de prednisona al dia por la mañana y precisa colocación de 4 implantes. ¿Cuál de las siguientes actuaciones no es necesaria?</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>En una paciente con una enfermedad autoinmune que toma 7.5mg de prednisona al día por la mañana y precisa colocación de 4 implantes. ¿Cuál de las siguientes actuaciones no es necesaria?</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="n">
+        <v>1260</v>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>pregunta</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>Ante qué patología pautaria una profilaxis antibiótica?</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>Ante qué patología pautaría una profilaxis antibiótica?</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="n">
+        <v>1260</v>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>opcion A</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>Prótesis valvular cardiaca</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>Prótesis valvular cardíaca</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="n">
+        <v>1260</v>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>soplo cardiaco funcional</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>soplo cardíaco funcional</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="n">
+        <v>1264</v>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>opcion D</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>La pauta antibiótica adecuada para prevenirla ante un proceso cruento odontologico es: Amoxicilina/Clavulánico 2gr 12h durante 10 dias+enjuague de clorhexidina al 0.12% o Clindamicina 300 mg 1 comprimido cada 8 h durante 10 días y ciprofloxacina 500mg/12h durante 10 dias+enjuague de clorhexidina al 0.12%</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>La pauta antibiótica adecuada para prevenirla ante un proceso cruento odontologico es: Amoxicilina/Clavulánico 2gr 12h durante 10 días+enjuague de clorhexidina al 0.12% o Clindamicina 300 mg 1 comprimido cada 8 h durante 10 días y ciprofloxacina 500mg/12h durante 10 días+enjuague de clorhexidina al 0.12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="n">
+        <v>1266</v>
+      </c>
+      <c r="B142" s="7" t="inlineStr">
+        <is>
+          <t>opcion C</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="inlineStr">
+        <is>
+          <t>Debe realizarse un legrado correcto del alveolo.</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>Debe realizarse un legrado correcto del alvéolo.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Por qué no hice una corrección ortográfica general (más allá de tildes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>El corrector (hunspell, diccionario es_ES) marca como 'error' miles de palabras del banco que en realidad están bien escritas — simplemente son vocabulario médico/odontológico que el diccionario general no conoce. Cuando eso pasa, sugiere la palabra real más parecida por edición de texto, sin entender el significado. Estos son ejemplos reales que salieron al correrlo sobre este banco:</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Palabra en el banco</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Sugerencia del corrector</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Por qué aplicarla sería un error</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>don</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>síndrome de Down → quedaría "síndrome de don": borra la referencia al síndrome</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>hipertiroidismo</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>hipotiroidismo</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>invierte el diagnóstico (hiper→hipo), sentido clínico opuesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>necrotizante</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>erotizante</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>"fascitis necrotizante" → "fascitis erotizante": palabra real pero sin relación</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>codeína</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>condena</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>nombre de fármaco → palabra común no relacionada</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>aórtica</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>caótica</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>término anatómico → adjetivo no relacionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>hemorrágica</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>hemorragia</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>adjetivo correcto que el diccionario no reconoce, no es un error</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>En total, sobre las ~5.400 palabras únicas del banco (sin contar siglas en mayúscula), el corrector marcó unas 1.340 como</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>'desconocidas'. La gran mayoría son términos técnicos correctos (nombres de fármacos, patologías, epónimos). Filtrar cuáles</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>de esas 1.340 son errores reales de tipeo requiere criterio médico, no solo comparación de texto — por eso preferí no aplicar</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>nada de esto automáticamente ni tampoco volcar la lista completa acá (sería más ruido que señal). Si en algún momento querés</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>una revisión ortográfica más a fondo, lo mejor sería que la haga alguien con formación en el tema, o que me pases un</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>glosario de términos válidos del banco para afinar el corrector.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="C5:C10"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>